--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:52</t>
+    <t xml:space="preserve">2026-09-10 01:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:02</t>
+    <t xml:space="preserve">2026-09-18 11:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:09</t>
+    <t xml:space="preserve">2026-09-23 14:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:33</t>
+    <t xml:space="preserve">2026-10-02 15:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2020_nuble.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Yungay</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">Quillón</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:57</t>
+    <t xml:space="preserve">2026-10-04 10:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:20</t>
+    <t xml:space="preserve">2026-10-05 15:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
